--- a/Day - 4 Funtions_Intro.xlsx
+++ b/Day - 4 Funtions_Intro.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\30_Days_Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FEE62AD-F152-4C3E-8DEC-84A3FA4B10FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E50CBB-8AB7-4CCD-BEE9-CBA936D66A2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{E8AEC2CD-2424-4959-AD65-BD24BDFEA33C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{E8AEC2CD-2424-4959-AD65-BD24BDFEA33C}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="2" r:id="rId1"/>
@@ -1994,11 +1994,11 @@
         <v>0</v>
       </c>
       <c r="L3" s="7" t="b">
-        <f t="shared" ref="L3:L12" si="0">$S$3&lt;=C3</f>
+        <f>$V$4&lt;=C3</f>
         <v>1</v>
       </c>
       <c r="M3" s="7" t="b">
-        <f t="shared" ref="M3:M12" si="1">$G3&gt;=$S$4</f>
+        <f>$V$5&lt;=$D3</f>
         <v>1</v>
       </c>
       <c r="N3" s="7">
@@ -2032,48 +2032,48 @@
         <v>12000</v>
       </c>
       <c r="F4" s="7">
-        <f t="shared" ref="F4:F12" si="2">C4</f>
+        <f t="shared" ref="F4:F12" si="0">C4</f>
         <v>4</v>
       </c>
       <c r="G4" s="7">
-        <f t="shared" ref="G4:G12" si="3">D4+E4</f>
+        <f t="shared" ref="G4:G12" si="1">D4+E4</f>
         <v>147000</v>
       </c>
       <c r="H4" s="8">
-        <f t="shared" ref="H4:H12" si="4">E4/D4</f>
+        <f t="shared" ref="H4:H12" si="2">E4/D4</f>
         <v>8.8888888888888892E-2</v>
       </c>
       <c r="I4" s="9">
-        <f t="shared" ref="I4:I12" si="5">D4+D4*H4</f>
+        <f t="shared" ref="I4:I12" si="3">D4+D4*H4</f>
         <v>147000</v>
       </c>
       <c r="J4" s="7" t="b">
-        <f t="shared" ref="J4:J12" si="6">G4=I4</f>
+        <f t="shared" ref="J4:J12" si="4">G4=I4</f>
         <v>1</v>
       </c>
       <c r="K4" s="7" t="b">
-        <f t="shared" ref="K4:K12" si="7">E4&gt;D4</f>
+        <f t="shared" ref="K4:K12" si="5">E4&gt;D4</f>
         <v>0</v>
       </c>
       <c r="L4" s="7" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" ref="L4:L12" si="6">$V$4&lt;=C4</f>
+        <v>0</v>
       </c>
       <c r="M4" s="7" t="b">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="M4:M12" si="7">$V$5&lt;=$D4</f>
         <v>1</v>
       </c>
       <c r="N4" s="7">
         <f t="shared" ref="N4:N12" si="8">L4*M4</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" s="7" t="b">
         <f t="shared" ref="O4:O12" si="9">L4*M4=1</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" s="7" t="b">
         <f t="shared" ref="P4:P12" si="10">AND(L4,M4)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4" s="3" t="s">
         <v>26</v>
@@ -2096,48 +2096,48 @@
         <v>5000</v>
       </c>
       <c r="F5" s="7">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G5" s="7">
+        <f t="shared" si="1"/>
+        <v>80000</v>
+      </c>
+      <c r="H5" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="G5" s="7">
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="I5" s="9">
         <f t="shared" si="3"/>
         <v>80000</v>
       </c>
-      <c r="H5" s="8">
+      <c r="J5" s="7" t="b">
         <f t="shared" si="4"/>
-        <v>6.6666666666666666E-2</v>
-      </c>
-      <c r="I5" s="9">
+        <v>1</v>
+      </c>
+      <c r="K5" s="7" t="b">
         <f t="shared" si="5"/>
-        <v>80000</v>
-      </c>
-      <c r="J5" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" s="7" t="b">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="K5" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="M5" s="7" t="b">
         <f t="shared" si="7"/>
         <v>0</v>
-      </c>
-      <c r="L5" s="7" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M5" s="7" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
       </c>
       <c r="N5" s="7">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" s="7" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" s="7" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5" s="5" t="s">
         <v>27</v>
@@ -2160,35 +2160,35 @@
         <v>8000</v>
       </c>
       <c r="F6" s="7">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G6" s="7">
+        <f t="shared" si="1"/>
+        <v>118000</v>
+      </c>
+      <c r="H6" s="8">
         <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-      <c r="G6" s="7">
+        <v>7.2727272727272724E-2</v>
+      </c>
+      <c r="I6" s="9">
         <f t="shared" si="3"/>
         <v>118000</v>
       </c>
-      <c r="H6" s="8">
+      <c r="J6" s="7" t="b">
         <f t="shared" si="4"/>
-        <v>7.2727272727272724E-2</v>
-      </c>
-      <c r="I6" s="9">
+        <v>1</v>
+      </c>
+      <c r="K6" s="7" t="b">
         <f t="shared" si="5"/>
-        <v>118000</v>
-      </c>
-      <c r="J6" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" s="7" t="b">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="K6" s="7" t="b">
+      <c r="M6" s="7" t="b">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L6" s="7" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M6" s="7" t="b">
-        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="N6" s="7">
@@ -2218,48 +2218,48 @@
         <v>11000</v>
       </c>
       <c r="F7" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G7" s="7">
+        <f t="shared" si="1"/>
+        <v>136000</v>
+      </c>
+      <c r="H7" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="G7" s="7">
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="I7" s="9">
         <f t="shared" si="3"/>
         <v>136000</v>
       </c>
-      <c r="H7" s="8">
+      <c r="J7" s="7" t="b">
         <f t="shared" si="4"/>
-        <v>8.7999999999999995E-2</v>
-      </c>
-      <c r="I7" s="9">
+        <v>1</v>
+      </c>
+      <c r="K7" s="7" t="b">
         <f t="shared" si="5"/>
-        <v>136000</v>
-      </c>
-      <c r="J7" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" s="7" t="b">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="K7" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="M7" s="7" t="b">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L7" s="7" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M7" s="7" t="b">
-        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="N7" s="7">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" s="7" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" s="7" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.3">
@@ -2276,35 +2276,35 @@
         <v>7000</v>
       </c>
       <c r="F8" s="7">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="G8" s="7">
+        <f t="shared" si="1"/>
+        <v>97000</v>
+      </c>
+      <c r="H8" s="8">
         <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-      <c r="G8" s="7">
+        <v>7.7777777777777779E-2</v>
+      </c>
+      <c r="I8" s="9">
         <f t="shared" si="3"/>
         <v>97000</v>
       </c>
-      <c r="H8" s="8">
+      <c r="J8" s="7" t="b">
         <f t="shared" si="4"/>
-        <v>7.7777777777777779E-2</v>
-      </c>
-      <c r="I8" s="9">
+        <v>1</v>
+      </c>
+      <c r="K8" s="7" t="b">
         <f t="shared" si="5"/>
-        <v>97000</v>
-      </c>
-      <c r="J8" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" s="7" t="b">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="K8" s="7" t="b">
+      <c r="M8" s="7" t="b">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L8" s="7" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M8" s="7" t="b">
-        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="N8" s="7">
@@ -2334,35 +2334,35 @@
         <v>15000</v>
       </c>
       <c r="F9" s="7">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="G9" s="7">
+        <f t="shared" si="1"/>
+        <v>165000</v>
+      </c>
+      <c r="H9" s="8">
         <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="G9" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="I9" s="9">
         <f t="shared" si="3"/>
         <v>165000</v>
       </c>
-      <c r="H9" s="8">
+      <c r="J9" s="7" t="b">
         <f t="shared" si="4"/>
-        <v>0.1</v>
-      </c>
-      <c r="I9" s="9">
+        <v>1</v>
+      </c>
+      <c r="K9" s="7" t="b">
         <f t="shared" si="5"/>
-        <v>165000</v>
-      </c>
-      <c r="J9" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" s="7" t="b">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="K9" s="7" t="b">
+      <c r="M9" s="7" t="b">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L9" s="7" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M9" s="7" t="b">
-        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="N9" s="7">
@@ -2392,35 +2392,35 @@
         <v>13000</v>
       </c>
       <c r="F10" s="7">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="G10" s="7">
+        <f t="shared" si="1"/>
+        <v>143000</v>
+      </c>
+      <c r="H10" s="8">
         <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="G10" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="I10" s="9">
         <f t="shared" si="3"/>
         <v>143000</v>
       </c>
-      <c r="H10" s="8">
+      <c r="J10" s="7" t="b">
         <f t="shared" si="4"/>
-        <v>0.1</v>
-      </c>
-      <c r="I10" s="9">
+        <v>1</v>
+      </c>
+      <c r="K10" s="7" t="b">
         <f t="shared" si="5"/>
-        <v>143000</v>
-      </c>
-      <c r="J10" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" s="7" t="b">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="K10" s="7" t="b">
+      <c r="M10" s="7" t="b">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L10" s="7" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M10" s="7" t="b">
-        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="N10" s="7">
@@ -2450,48 +2450,48 @@
         <v>14000</v>
       </c>
       <c r="F11" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G11" s="7">
+        <f t="shared" si="1"/>
+        <v>154000</v>
+      </c>
+      <c r="H11" s="8">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="G11" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="I11" s="9">
         <f t="shared" si="3"/>
         <v>154000</v>
       </c>
-      <c r="H11" s="8">
+      <c r="J11" s="7" t="b">
         <f t="shared" si="4"/>
-        <v>0.1</v>
-      </c>
-      <c r="I11" s="9">
+        <v>1</v>
+      </c>
+      <c r="K11" s="7" t="b">
         <f t="shared" si="5"/>
-        <v>154000</v>
-      </c>
-      <c r="J11" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" s="7" t="b">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="K11" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="M11" s="7" t="b">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L11" s="7" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M11" s="7" t="b">
-        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="N11" s="7">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" s="7" t="b">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P11" s="7" t="b">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.3">
@@ -2508,35 +2508,35 @@
         <v>9000</v>
       </c>
       <c r="F12" s="7">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="G12" s="7">
+        <f t="shared" si="1"/>
+        <v>124000</v>
+      </c>
+      <c r="H12" s="8">
         <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="G12" s="7">
+        <v>7.8260869565217397E-2</v>
+      </c>
+      <c r="I12" s="9">
         <f t="shared" si="3"/>
         <v>124000</v>
       </c>
-      <c r="H12" s="8">
+      <c r="J12" s="7" t="b">
         <f t="shared" si="4"/>
-        <v>7.8260869565217397E-2</v>
-      </c>
-      <c r="I12" s="9">
+        <v>1</v>
+      </c>
+      <c r="K12" s="7" t="b">
         <f t="shared" si="5"/>
-        <v>124000</v>
-      </c>
-      <c r="J12" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" s="7" t="b">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="K12" s="7" t="b">
+      <c r="M12" s="7" t="b">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L12" s="7" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M12" s="7" t="b">
-        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="N12" s="7">
